--- a/data/raw/commercial_real_estate_monthly.xlsx
+++ b/data/raw/commercial_real_estate_monthly.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRE Monthly" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CRE Monthly'!$A$1:$K$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CRE Monthly'!$A$1:$K$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,18 +445,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
   </cols>
@@ -464,27 +464,27 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Report Month</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Case</t>
+          <t>Plan Case</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>NII</t>
+          <t>Net Interest Income</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Orig Fee</t>
+          <t>Origination Fees</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Prepay Fee</t>
+          <t>Prepayment Fees</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Opex</t>
+          <t>Operating Costs</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -847,9 +847,7 @@
       <c r="D10" s="3" t="n">
         <v>0.801</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0.227</v>
-      </c>
+      <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="n">
         <v>0.348</v>
       </c>
@@ -1189,7 +1187,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t xml:space="preserve"> budget </t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1348,9 +1346,6 @@
           <t>Budget</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>6.41</v>
-      </c>
       <c r="D23" t="n">
         <v>0.791</v>
       </c>
@@ -1718,7 +1713,7 @@
         <v>0.452</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.139</v>
+        <v>32.085</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>1894.634</v>
@@ -1852,7 +1847,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t xml:space="preserve"> forecast </t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2210,7 +2205,7 @@
         <v>6.041</v>
       </c>
       <c r="D45" t="n">
-        <v>0.742</v>
+        <v>13.356</v>
       </c>
       <c r="E45" t="n">
         <v>0.207</v>
@@ -2858,8 +2853,125 @@
         <v>21.945</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>6.523</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>1952.86</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>20.771</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6.291</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.132</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1887.394</v>
+      </c>
+      <c r="K63" t="n">
+        <v>19.76</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>2.242</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>2052.153</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>21.904</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K61"/>
+  <autoFilter ref="A1:K64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>